--- a/reports/셀린느/history/2026-04-17/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/history/2026-04-17/셀린느_training_mgf_report.xlsx
@@ -1491,6 +1491,15 @@
     <t>2291조 1697억 43만</t>
   </si>
   <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1407조 6499억 5640만</t>
+  </si>
+  <si>
     <t>말레이히어로</t>
   </si>
   <si>
@@ -1500,15 +1509,6 @@
     <t>1394조 1932억 8825만</t>
   </si>
   <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1351조 3377억 9806만</t>
-  </si>
-  <si>
     <t>빌런투킬</t>
   </si>
   <si>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>162조 1649억 2915만</t>
+    <t>162조 5886억 9598만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>42조 7791억 4344만</t>
+    <t>43조 9302억 789만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1671,6 +1671,15 @@
     <t>35조 3962억 1100만</t>
   </si>
   <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>32조 6412억 5256만</t>
+  </si>
+  <si>
     <t>대방어조아</t>
   </si>
   <si>
@@ -1702,15 +1711,6 @@
   </si>
   <si>
     <t>29조 2978억 7327만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>28조 3643억 3420만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -7153,7 +7153,7 @@
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>92</v>
@@ -7185,7 +7185,7 @@
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>92</v>
@@ -7793,10 +7793,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>548</v>
@@ -7825,10 +7825,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>551</v>
@@ -7857,10 +7857,10 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>554</v>
@@ -7877,25 +7877,25 @@
         <v>47</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>555</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>555</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7909,22 +7909,22 @@
         <v>54</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>557</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>557</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>558</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>559</v>
